--- a/classification_results.xlsx
+++ b/classification_results.xlsx
@@ -1,14 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YOLO Results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ResNet Results" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="YOLO Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ResNet Results" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="YOLO Confusion Matrix" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ResNet Confusion Matrix" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +20,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -135,6 +125,66 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7620000" cy="5715000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7620000" cy="5715000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -426,56 +476,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>accuracy</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>actual_class</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>confidence</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>image_path</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>inference_speed_ms</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>postprocess_speed_ms</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>predicted_class</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>preprocess_speed_ms</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>total_accuracy</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>total_speed</t>
         </is>
@@ -483,61 +533,61 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>pothole</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>static\result\yolo\predicted_pothole-Pothole_0010.jpg</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="F2" t="n">
         <v>0</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>crack</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>99.81</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>static/result/yolo/predicted_pothole-crack3.jpg</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>402.6</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.1</v>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>pothole</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>962.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>33.33</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>1063.2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>crack</t>
+          <t>pothole</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>100</v>
+        <v>99.81</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>static/result/yolo/predicted_pothole-crack2.jpg</t>
+          <t>static\result\yolo\predicted_pothole-Pothole_0036.jpg</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>648.1</v>
+        <v>18.8</v>
       </c>
       <c r="F3" t="n">
         <v>0.1</v>
@@ -548,39 +598,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>582.4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>100</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>crack</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>75.09999999999999</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>static/result/yolo/predicted_crack-crack1.jpg</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>crack</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>710.5</v>
+        <v>10.5</v>
       </c>
     </row>
   </sheetData>
@@ -594,46 +612,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>accuracy</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>actual_class</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>confidence</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>image_path</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>inference_time</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>predicted_class</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>total_accuracy</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>total_speed</t>
         </is>
@@ -645,30 +663,30 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>pothole</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>static\result\resnet\predicted_crack-Pothole_0010.jpg</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1049.8</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>crack</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>97.41</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>static/result/resnet/predicted_pothole-crack3.jpg</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>1528.1</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>pothole</t>
         </is>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>4959.6</v>
+        <v>2155.2</v>
       </c>
     </row>
     <row r="3">
@@ -677,53 +695,55 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>pothole</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>99.98</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>static\result\resnet\predicted_crack-Pothole_0036.jpg</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1105.4</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>crack</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>59.75</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>static/result/resnet/predicted_pothole-crack2.jpg</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>1926.9</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>pothole</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>crack</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>99.44</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>static/result/resnet/predicted_pothole-crack1.jpg</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>1504.6</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>pothole</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>